--- a/all_product_config20260629.xlsx
+++ b/all_product_config20260629.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -584,6 +584,16 @@
           <t>note</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>time_decay</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>verified_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>[仓储费]季节:5/1-10/31为0.5、11/1-4/30为0.4</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -704,6 +719,11 @@
           <t>20251023新增</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -765,6 +785,11 @@
           <t>[仓储费]0.016元/千克·天(单位元/千克) [转抛]仓单长期有效、无强制注销月</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -826,6 +851,11 @@
           <t>[仓储费]完税货场0.4;保税另:库房0.6/货场0.5</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -887,6 +917,11 @@
           <t>[仓储费]仓库室内0.4/室外0.3、厂库0.25,取最高0.4 [转抛]仓单按生产日计180天有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -948,6 +983,11 @@
           <t>[转抛]含车(船)板交割→不可转抛</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1009,6 +1049,11 @@
           <t>[仓储费]1.8元/千克·天=0.0018元/克·天(单位元/克)</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1070,6 +1115,11 @@
           <t>[转抛]每月注销→不可转抛</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1131,6 +1181,11 @@
           <t>[仓储费]单位为元/张:0.035元/张·天</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1192,6 +1247,11 @@
           <t>[仓储费]库房0.5/货场0.4(保税),取最高0.5</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1253,6 +1313,11 @@
           <t>[仓储费]仓库1.4/厂库1.3,取最高1.4 [转抛]仓单有效期生产次年6月30日且入库限六个月、双重规则保守取不可转抛</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1314,6 +1379,11 @@
           <t>[仓储费]仓库1.5/厂库1.2</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1370,6 +1440,11 @@
           <t>BZ2603</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1431,6 +1506,11 @@
           <t>20250714更新，添加新品种 [仓储费]季节:5/1-10/31为0.6、11/1-4/30为0.5</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1489,7 +1569,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20250714更新，注销月只有11月。仓储费新疆0.6其他0.8. [仓储费]新疆0.6/非新疆0.8,取最高0.8</t>
+          <t>20250714更新，注销月只有11月。仓储费新疆0.6其他0.8. [仓储费]新疆0.6/非新疆0.8,取最高0.8 [时间贴水]旧棉自N+1年8月1日起每日历日贴水4元/吨,至11月第15交易日(郑商所棉花业务细则);to取11-21为日历近似</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>[{"per_day": 4, "from": "08-01", "to": "11-21"}]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1640,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[仓储费]新疆3/内地2.5,取最高3 [转抛]可转抛,但交易所曾限制转抛数量需注意</t>
+          <t>[仓储费]新疆3/内地2.5,取最高3 [转抛]可转抛,但交易所曾限制转抛数量需注意 [时间贴水]上一生产年度红枣仅可车船板贴水交割新年度12/1/3月:12月100、1月150、3月300元/吨(2024-12修订细则),增量编码跨12/20+50、跨2/1+150;旧枣不可注册仓单,新枣仓单转抛不付此贴水(保守计入)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[{"step": "12-20", "amount": 50}, {"step": "02-01", "amount": 150}]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1609,6 +1709,11 @@
           <t>CS2311</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1670,6 +1775,11 @@
           <t>[仓储费]完税货场0.3;保税另:库房0.5/货场0.4</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1726,6 +1836,11 @@
           <t>CY2401</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1787,6 +1902,11 @@
           <t>[转抛]每月注销→不可转抛</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1845,6 +1965,11 @@
           <t>[转抛]现金交割无仓单→不可转抛</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1901,6 +2026,11 @@
           <t>EG2401</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1962,6 +2092,11 @@
           <t>[仓储费]单位为元/立方米:1元/立方米·天</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2023,6 +2158,11 @@
           <t>[转抛]仅厂库交割,但作可转抛</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2084,6 +2224,11 @@
           <t>[仓储费]1.4(上期发[2021]153号,2021/6/4起)</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2145,6 +2290,11 @@
           <t>[转抛]仓单按生产日计360天有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2201,6 +2351,11 @@
           <t>I2401</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2262,6 +2417,11 @@
           <t>IC2310</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2323,6 +2483,11 @@
           <t>IF2310</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2384,6 +2549,11 @@
           <t>IH2310</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2445,6 +2615,11 @@
           <t>IM2310</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2501,6 +2676,11 @@
           <t>J2401</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2562,6 +2742,11 @@
           <t>[转抛]每月注销、含车(船)板→不可转抛</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2620,7 +2805,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>[转抛]每月注销→不可转抛</t>
+          <t>[转抛]每月注销→不可转抛 [规则断层]jm2701起交割标准大幅提高(2026-07用户确认),跨2612/2701的价差/蝶式结构偏移为正常,勿当折角机会</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -2684,6 +2874,11 @@
           <t>[仓储费]季节:10/1-次年4/30为0.5、5/1-9/30为0.55(含保险费),取最高0.55</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2740,6 +2935,11 @@
           <t>L2401</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -2796,6 +2996,11 @@
           <t>LC2401</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -2857,6 +3062,11 @@
           <t>[仓储费]单位为元/立方米:0.6元/立方米·天 [转抛]含车(船)板、仅厂库→不可转抛</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -2918,6 +3128,11 @@
           <t>[转抛]每月注销、含车(船)板、仅厂库→不可转抛</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2979,6 +3194,11 @@
           <t>[仓储费]季节:10/1-次年4/30为0.5、5/1-9/30为0.55(含保险费),取最高0.55</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3040,6 +3260,11 @@
           <t>[仓储费]1.4</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3096,6 +3321,11 @@
           <t>M2401</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3152,6 +3382,11 @@
           <t>MA2401</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3208,6 +3443,11 @@
           <t>NI2310</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -3269,6 +3509,11 @@
           <t>[转抛]仓单按报关/生产日计有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -3323,6 +3568,11 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>OI2401</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3384,6 +3634,11 @@
           <t>20251023新增。含厂库交割，仓单有效期12个月。 [仓储费]上期所厂库仓储租金0.9元/吨·天</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -3445,6 +3700,11 @@
           <t>[转抛]每月注销→不可转抛</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -3501,6 +3761,11 @@
           <t>PB2310</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -3552,6 +3817,11 @@
           <t>20251223新增 [注销月]仓库仓单长期有效、厂库每年8月统一注销；保守按厂库记注销月8月</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -3613,6 +3883,11 @@
           <t>20251023更新 PF2510起，注销月改为36912</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -3674,6 +3949,11 @@
           <t>[转抛]仅厂库交割,但作可转抛</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -3733,6 +4013,11 @@
       <c r="O54" t="inlineStr">
         <is>
           <t>[转抛]含车(船)板、仅厂库→不可转抛</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3794,6 +4079,11 @@
           <t>20251023新增</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -3855,6 +4145,11 @@
           <t>[转抛]含车(船)板交割→不可转抛</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -3911,6 +4206,11 @@
           <t>PP2401</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -3967,6 +4267,11 @@
           <t>PR2503</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4026,6 +4331,11 @@
       </c>
       <c r="N59" s="3" t="n"/>
       <c r="O59" s="3" t="n"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -4077,6 +4387,11 @@
           <t>20251223新增 [注销月]仓库仓单长期有效、厂库每年8月统一注销；保守按厂库记注销月8月</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -4133,6 +4448,11 @@
           <t>PX2405</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -4194,6 +4514,11 @@
           <t>[转抛]仓单按生产日计90天有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -4250,6 +4575,11 @@
           <t>RI2401</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -4306,6 +4636,11 @@
           <t>RM2401</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -4367,6 +4702,11 @@
           <t>[转抛]每月注销→不可转抛</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -4428,6 +4768,11 @@
           <t>[转抛]含车(船)板交割→不可转抛</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -4489,6 +4834,11 @@
           <t>[仓储费]1.3 [转抛]进口仓单按注册日计18个月有效期(国产按月)、双重规则保守取不可转抛</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -4545,6 +4895,11 @@
           <t>SA2401</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -4606,6 +4961,11 @@
           <t>[仓储费]单位元/桶:0.2元/桶·天(2022/1/1起执行)</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -4662,6 +5022,11 @@
           <t>SF2311</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="71" customFormat="1" s="3">
       <c r="A71" s="4" t="inlineStr">
@@ -4723,6 +5088,11 @@
           <t>202602开始修改仓储费由2.5湿吨天到1.5-1.8湿吨天 [仓储费]5.4为干吨口径;湿吨约1.8(2026/2起1.5-1.8),约32%纯度,干吨≈湿吨×3(1.8×3≈5.4)</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -4779,6 +5149,11 @@
           <t>SI2311</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -4835,6 +5210,11 @@
           <t>SM2311</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -4891,6 +5271,11 @@
           <t>SN2310</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -4952,6 +5337,11 @@
           <t>[仓储费]仓库0.8/厂库0.7 [转抛]厂库仓单按注册日计有效期(国产按月)、双重规则保守取不可转抛</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -5008,6 +5398,21 @@
           <t>SR2401</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>[时间贴水]N制糖年度白糖自当年9月合约交割起每交割月增贴水20元/吨(9月20/11月40,细则第二十五条);按step编码:跨8/1+20、跨10/1+20</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>[{"step": "08-01", "amount": 20}, {"step": "10-01", "amount": 20}]</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -5069,6 +5474,11 @@
           <t>[转抛]仓单按生产日计360/315天有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -5127,6 +5537,11 @@
           <t>[转抛]国债无标准仓单(可交割券)→不可转抛</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -5183,6 +5598,11 @@
           <t>TA2401</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -5241,6 +5661,11 @@
           <t>[转抛]国债无标准仓单(可交割券)→不可转抛</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -5299,6 +5724,11 @@
           <t>[转抛]国债无标准仓单(可交割券)→不可转抛</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -5357,6 +5787,11 @@
           <t>[转抛]国债无标准仓单(可交割券)→不可转抛</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -5413,6 +5848,11 @@
           <t>UR2401</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="84" customFormat="1" s="3">
       <c r="A84" s="5" t="inlineStr">
@@ -5469,6 +5909,11 @@
           <t>V2401</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="85" customFormat="1" s="3">
       <c r="A85" s="5" t="inlineStr">
@@ -5530,6 +5975,11 @@
           <t>[仓储费]0.5(服务机构直接收取) [转抛]含车(船)板、无标准仓单→不可转抛</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="86" customFormat="1" s="3">
       <c r="A86" s="5" t="inlineStr">
@@ -5591,6 +6041,11 @@
           <t>[转抛]仓单按生产日计90天有效期、无固定注销月→不可转抛</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="87" customFormat="1" s="3">
       <c r="A87" s="5" t="inlineStr">
@@ -5647,6 +6102,11 @@
           <t>Y2401</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -5708,6 +6168,11 @@
           <t>[转抛]含车(船)板、仅厂库→不可转抛</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -5762,6 +6227,11 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>ZN2310</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
